--- a/data/trans_dic/IP22D5_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP22D5_R_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2091</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2552</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2765</t>
+          <t>0; 1996</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2435</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2785</t>
+          <t>0; 2494</t>
         </is>
       </c>
     </row>
